--- a/database/event/5506/event_5506_evp_summary.xlsx
+++ b/database/event/5506/event_5506_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.2562</v>
+        <v>10.2355</v>
       </c>
       <c r="C2" t="n">
-        <v>5.0584</v>
+        <v>5.0482</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7219</v>
+        <v>3.6339</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2562</v>
+        <v>10.2355</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2425</v>
+        <v>4.2218</v>
       </c>
       <c r="G2" t="n">
         <v>6.0137</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3492</v>
+        <v>4.3168</v>
       </c>
       <c r="I2" t="n">
         <v>4.3897</v>
@@ -548,7 +548,7 @@
         <v>4.8879</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5823</v>
+        <v>3.5044</v>
       </c>
       <c r="E3" t="n">
         <v>9.910500000000001</v>
@@ -594,7 +594,7 @@
         <v>4.6708</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4045</v>
+        <v>3.3291</v>
       </c>
       <c r="E4" t="n">
         <v>9.4704</v>
@@ -640,7 +640,7 @@
         <v>4.2554</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0642</v>
+        <v>2.9935</v>
       </c>
       <c r="E5" t="n">
         <v>8.628</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.8427</v>
+        <v>7.8196</v>
       </c>
       <c r="C6" t="n">
-        <v>3.868</v>
+        <v>3.8566</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7469</v>
+        <v>2.6714</v>
       </c>
       <c r="E6" t="n">
-        <v>7.8427</v>
+        <v>7.8196</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5591</v>
+        <v>4.5361</v>
       </c>
       <c r="G6" t="n">
         <v>3.2836</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8456</v>
+        <v>4.8095</v>
       </c>
       <c r="I6" t="n">
         <v>4.8908</v>
@@ -732,7 +732,7 @@
         <v>3.7285</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6326</v>
+        <v>2.5679</v>
       </c>
       <c r="E7" t="n">
         <v>7.5597</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.449</v>
+        <v>5.4203</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6875</v>
+        <v>2.6733</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7799</v>
+        <v>1.7155</v>
       </c>
       <c r="E8" t="n">
-        <v>5.449</v>
+        <v>5.4203</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8444</v>
+        <v>3.8157</v>
       </c>
       <c r="G8" t="n">
         <v>1.6046</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8444</v>
+        <v>3.8157</v>
       </c>
       <c r="I8" t="n">
         <v>3.8802</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.9317</v>
+        <v>4.9039</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4323</v>
+        <v>2.4186</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5709</v>
+        <v>1.5098</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9317</v>
+        <v>4.9039</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7283</v>
+        <v>3.7005</v>
       </c>
       <c r="G9" t="n">
         <v>1.2034</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7283</v>
+        <v>3.7005</v>
       </c>
       <c r="I9" t="n">
         <v>3.7631</v>
@@ -870,7 +870,7 @@
         <v>2.2778</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4443</v>
+        <v>1.396</v>
       </c>
       <c r="E10" t="n">
         <v>4.6183</v>
@@ -916,7 +916,7 @@
         <v>2.1842</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3677</v>
+        <v>1.3204</v>
       </c>
       <c r="E11" t="n">
         <v>4.4286</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.3993</v>
+        <v>4.3435</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1697</v>
+        <v>2.1422</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3559</v>
+        <v>1.2865</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3993</v>
+        <v>4.3435</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2291</v>
+        <v>5.1733</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8298</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8962</v>
+        <v>5.8087</v>
       </c>
       <c r="I12" t="n">
         <v>6.0067</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.3029</v>
+        <v>4.2947</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1222</v>
+        <v>2.1182</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3169</v>
+        <v>1.2671</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3029</v>
+        <v>4.2947</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1767</v>
+        <v>2.1685</v>
       </c>
       <c r="G13" t="n">
         <v>2.1262</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1767</v>
+        <v>2.1685</v>
       </c>
       <c r="I13" t="n">
         <v>2.1868</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.2587</v>
+        <v>4.2484</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1004</v>
+        <v>2.0953</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2991</v>
+        <v>1.2487</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2587</v>
+        <v>4.2484</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7497</v>
+        <v>2.7394</v>
       </c>
       <c r="G14" t="n">
         <v>1.509</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7497</v>
+        <v>2.7394</v>
       </c>
       <c r="I14" t="n">
         <v>2.7625</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0101</v>
+        <v>3.9519</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9778</v>
+        <v>1.9491</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1986</v>
+        <v>1.1305</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0101</v>
+        <v>3.9519</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0101</v>
+        <v>3.6194</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.3325</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0101</v>
+        <v>3.6194</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0853</v>
+        <v>3.6498</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.3325</v>
       </c>
       <c r="K15" t="n">
-        <v>371</v>
+        <v>308</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M15" t="n">
-        <v>4.0853</v>
+        <v>3.9823</v>
       </c>
       <c r="N15" t="n">
-        <v>371</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.9654</v>
+        <v>3.9506</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9557</v>
+        <v>1.9484</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1806</v>
+        <v>1.13</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9654</v>
+        <v>3.9506</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6329</v>
+        <v>3.9506</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3325</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6329</v>
+        <v>3.9506</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6498</v>
+        <v>4.0853</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3325</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="L16" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9823</v>
+        <v>4.0853</v>
       </c>
       <c r="N16" t="n">
-        <v>468</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.9499</v>
+        <v>3.8739</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9481</v>
+        <v>1.9106</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1743</v>
+        <v>1.0995</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9499</v>
+        <v>3.8739</v>
       </c>
       <c r="F17" t="n">
-        <v>5.5724</v>
+        <v>5.4964</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6225</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4345</v>
+        <v>6.3153</v>
       </c>
       <c r="I17" t="n">
         <v>6.5856</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.6952</v>
+        <v>3.6404</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8225</v>
+        <v>1.7955</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0714</v>
+        <v>1.0064</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6952</v>
+        <v>3.6404</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6952</v>
+        <v>3.6404</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6952</v>
+        <v>3.6404</v>
       </c>
       <c r="I18" t="n">
         <v>3.7645</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6626</v>
+        <v>3.6033</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8064</v>
+        <v>1.7772</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0582</v>
+        <v>0.9916</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6626</v>
+        <v>3.6033</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2033</v>
+        <v>3.144</v>
       </c>
       <c r="G19" t="n">
         <v>0.4593</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2033</v>
+        <v>3.144</v>
       </c>
       <c r="I19" t="n">
         <v>3.2786</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.5253</v>
+        <v>3.512</v>
       </c>
       <c r="C20" t="n">
-        <v>1.7387</v>
+        <v>1.7321</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0028</v>
+        <v>0.9553</v>
       </c>
       <c r="E20" t="n">
-        <v>3.5253</v>
+        <v>3.512</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7893</v>
+        <v>1.776</v>
       </c>
       <c r="G20" t="n">
         <v>1.736</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7893</v>
+        <v>1.776</v>
       </c>
       <c r="I20" t="n">
         <v>1.806</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.4768</v>
+        <v>3.4252</v>
       </c>
       <c r="C21" t="n">
-        <v>1.7148</v>
+        <v>1.6893</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9832</v>
+        <v>0.9207</v>
       </c>
       <c r="E21" t="n">
-        <v>3.4768</v>
+        <v>3.4252</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4768</v>
+        <v>3.4252</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4768</v>
+        <v>3.4252</v>
       </c>
       <c r="I21" t="n">
         <v>3.542</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.4443</v>
+        <v>3.3977</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6987</v>
+        <v>1.6758</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9701</v>
+        <v>0.9097</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4443</v>
+        <v>3.3977</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0795</v>
+        <v>4.0329</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6352</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0937</v>
+        <v>4.0329</v>
       </c>
       <c r="I22" t="n">
         <v>4.1704</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.3801</v>
+        <v>3.3424</v>
       </c>
       <c r="C23" t="n">
-        <v>1.6671</v>
+        <v>1.6485</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8877</v>
       </c>
       <c r="E23" t="n">
-        <v>3.3801</v>
+        <v>3.3424</v>
       </c>
       <c r="F23" t="n">
-        <v>3.3801</v>
+        <v>3.3424</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3801</v>
+        <v>3.3424</v>
       </c>
       <c r="I23" t="n">
         <v>3.4275</v>
@@ -1514,7 +1514,7 @@
         <v>1.5207</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8242</v>
+        <v>0.7845</v>
       </c>
       <c r="E24" t="n">
         <v>3.0833</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.0695</v>
+        <v>3.0627</v>
       </c>
       <c r="C25" t="n">
-        <v>1.5139</v>
+        <v>1.5105</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8186</v>
+        <v>0.7763</v>
       </c>
       <c r="E25" t="n">
-        <v>3.0695</v>
+        <v>3.0627</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8231</v>
+        <v>1.8163</v>
       </c>
       <c r="G25" t="n">
         <v>1.2464</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8231</v>
+        <v>1.8163</v>
       </c>
       <c r="I25" t="n">
         <v>1.8316</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.0558</v>
+        <v>3.0365</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5071</v>
+        <v>1.4976</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8131</v>
+        <v>0.7658</v>
       </c>
       <c r="E26" t="n">
-        <v>3.0558</v>
+        <v>3.0365</v>
       </c>
       <c r="F26" t="n">
-        <v>3.0558</v>
+        <v>0.4554</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.5811</v>
       </c>
       <c r="H26" t="n">
-        <v>3.0558</v>
+        <v>0.4554</v>
       </c>
       <c r="I26" t="n">
-        <v>3.0987</v>
+        <v>0.4631</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.5811</v>
       </c>
       <c r="K26" t="n">
-        <v>420</v>
+        <v>333</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M26" t="n">
-        <v>3.0987</v>
+        <v>3.0442</v>
       </c>
       <c r="N26" t="n">
-        <v>420</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.0399</v>
+        <v>3.0218</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4993</v>
+        <v>1.4904</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8067</v>
+        <v>0.76</v>
       </c>
       <c r="E27" t="n">
-        <v>3.0399</v>
+        <v>3.0218</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4588</v>
+        <v>3.0218</v>
       </c>
       <c r="G27" t="n">
-        <v>2.5811</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4588</v>
+        <v>3.0218</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4631</v>
+        <v>3.0987</v>
       </c>
       <c r="J27" t="n">
-        <v>2.5811</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>333</v>
+        <v>420</v>
       </c>
       <c r="L27" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.0442</v>
+        <v>3.0987</v>
       </c>
       <c r="N27" t="n">
-        <v>452</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>1.4237</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7448</v>
+        <v>0.7062</v>
       </c>
       <c r="E28" t="n">
         <v>2.8867</v>
@@ -1744,7 +1744,7 @@
         <v>1.3791</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7083</v>
+        <v>0.6701</v>
       </c>
       <c r="E29" t="n">
         <v>2.7963</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.7552</v>
+        <v>2.7491</v>
       </c>
       <c r="C30" t="n">
-        <v>1.3589</v>
+        <v>1.3559</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6917</v>
+        <v>0.6513</v>
       </c>
       <c r="E30" t="n">
-        <v>2.7552</v>
+        <v>2.7491</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8083</v>
+        <v>0.8022</v>
       </c>
       <c r="G30" t="n">
         <v>1.9469</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8083</v>
+        <v>0.8022</v>
       </c>
       <c r="I30" t="n">
         <v>0.8158</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.721</v>
+        <v>2.6998</v>
       </c>
       <c r="C31" t="n">
-        <v>1.342</v>
+        <v>1.3315</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6317</v>
       </c>
       <c r="E31" t="n">
-        <v>2.721</v>
+        <v>2.6998</v>
       </c>
       <c r="F31" t="n">
-        <v>2.8413</v>
+        <v>2.8201</v>
       </c>
       <c r="G31" t="n">
         <v>-0.1203</v>
       </c>
       <c r="H31" t="n">
-        <v>2.8413</v>
+        <v>2.8201</v>
       </c>
       <c r="I31" t="n">
         <v>2.8678</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.5514</v>
+        <v>2.523</v>
       </c>
       <c r="C32" t="n">
-        <v>1.2584</v>
+        <v>1.2444</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6093</v>
+        <v>0.5613</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5514</v>
+        <v>2.523</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5514</v>
+        <v>2.523</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.5514</v>
+        <v>2.523</v>
       </c>
       <c r="I32" t="n">
         <v>2.5872</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.3129</v>
+        <v>2.3003</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1407</v>
+        <v>1.1345</v>
       </c>
       <c r="D33" t="n">
-        <v>0.513</v>
+        <v>0.4725</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3129</v>
+        <v>2.3003</v>
       </c>
       <c r="F33" t="n">
-        <v>1.7009</v>
+        <v>1.6883</v>
       </c>
       <c r="G33" t="n">
         <v>0.612</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7009</v>
+        <v>1.6883</v>
       </c>
       <c r="I33" t="n">
         <v>1.7168</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.2189</v>
+        <v>2.2214</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0944</v>
+        <v>1.0956</v>
       </c>
       <c r="D34" t="n">
-        <v>0.475</v>
+        <v>0.4411</v>
       </c>
       <c r="E34" t="n">
-        <v>2.2189</v>
+        <v>2.2214</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3486</v>
+        <v>-0.3461</v>
       </c>
       <c r="G34" t="n">
         <v>2.5675</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3486</v>
+        <v>-0.3461</v>
       </c>
       <c r="I34" t="n">
         <v>-0.3519</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.2113</v>
+        <v>2.1785</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0906</v>
+        <v>1.0744</v>
       </c>
       <c r="D35" t="n">
-        <v>0.472</v>
+        <v>0.424</v>
       </c>
       <c r="E35" t="n">
-        <v>2.2113</v>
+        <v>2.1785</v>
       </c>
       <c r="F35" t="n">
-        <v>2.2113</v>
+        <v>2.1785</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.2113</v>
+        <v>2.1785</v>
       </c>
       <c r="I35" t="n">
         <v>2.2528</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.9944</v>
+        <v>1.9755</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9836</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3843</v>
+        <v>0.3431</v>
       </c>
       <c r="E36" t="n">
-        <v>1.9944</v>
+        <v>1.9755</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0218</v>
+        <v>1.0029</v>
       </c>
       <c r="G36" t="n">
         <v>0.9726</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0218</v>
+        <v>1.0029</v>
       </c>
       <c r="I36" t="n">
         <v>1.0458</v>
@@ -2112,7 +2112,7 @@
         <v>0.8748</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2952</v>
+        <v>0.2627</v>
       </c>
       <c r="E37" t="n">
         <v>1.7737</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.7138</v>
+        <v>1.7074</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8421</v>
       </c>
       <c r="D38" t="n">
-        <v>0.271</v>
+        <v>0.2363</v>
       </c>
       <c r="E38" t="n">
-        <v>1.7138</v>
+        <v>1.7074</v>
       </c>
       <c r="F38" t="n">
-        <v>1.71</v>
+        <v>1.7036</v>
       </c>
       <c r="G38" t="n">
         <v>0.0038</v>
       </c>
       <c r="H38" t="n">
-        <v>1.71</v>
+        <v>1.7036</v>
       </c>
       <c r="I38" t="n">
         <v>1.7179</v>
@@ -2204,7 +2204,7 @@
         <v>0.8211000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2512</v>
+        <v>0.2194</v>
       </c>
       <c r="E39" t="n">
         <v>1.6649</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.6406</v>
+        <v>1.6467</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8091</v>
+        <v>0.8122</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2414</v>
+        <v>0.2121</v>
       </c>
       <c r="E40" t="n">
-        <v>1.6406</v>
+        <v>1.6467</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="G40" t="n">
         <v>2.4637</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>-0.8308</v>
@@ -2296,7 +2296,7 @@
         <v>0.739</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1839</v>
+        <v>0.153</v>
       </c>
       <c r="E41" t="n">
         <v>1.4983</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.4521</v>
+        <v>1.4448</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7126</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1653</v>
+        <v>0.1317</v>
       </c>
       <c r="E42" t="n">
-        <v>1.4521</v>
+        <v>1.4448</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9856</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="G42" t="n">
         <v>0.4665</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9856</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="I42" t="n">
         <v>0.9948</v>
@@ -2388,7 +2388,7 @@
         <v>0.6796</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1353</v>
+        <v>0.105</v>
       </c>
       <c r="E43" t="n">
         <v>1.3779</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1825</v>
+        <v>1.1501</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5672</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0563</v>
+        <v>0.0143</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1825</v>
+        <v>1.1501</v>
       </c>
       <c r="F44" t="n">
-        <v>2.1868</v>
+        <v>2.1544</v>
       </c>
       <c r="G44" t="n">
         <v>-1.0043</v>
       </c>
       <c r="H44" t="n">
-        <v>2.1868</v>
+        <v>2.1544</v>
       </c>
       <c r="I44" t="n">
         <v>2.2278</v>
@@ -2480,7 +2480,7 @@
         <v>0.5329</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0151</v>
+        <v>-0.0135</v>
       </c>
       <c r="E45" t="n">
         <v>1.0804</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8888</v>
+        <v>0.8891</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4384</v>
+        <v>0.4385</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0623</v>
+        <v>-0.0897</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8888</v>
+        <v>0.8891</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0417</v>
+        <v>-0.0414</v>
       </c>
       <c r="G46" t="n">
         <v>0.9305</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0417</v>
+        <v>-0.0414</v>
       </c>
       <c r="I46" t="n">
         <v>-0.0421</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.875</v>
+        <v>0.8689</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4316</v>
+        <v>0.4285</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0679</v>
+        <v>-0.0977</v>
       </c>
       <c r="E47" t="n">
-        <v>0.875</v>
+        <v>0.8689</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3304</v>
+        <v>0.3243</v>
       </c>
       <c r="G47" t="n">
         <v>0.5446</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3304</v>
+        <v>0.3243</v>
       </c>
       <c r="I47" t="n">
         <v>0.3382</v>
@@ -2618,7 +2618,7 @@
         <v>0.2546</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2128</v>
+        <v>-0.2382</v>
       </c>
       <c r="E48" t="n">
         <v>0.5163</v>
@@ -2664,7 +2664,7 @@
         <v>0.1492</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2991</v>
+        <v>-0.3234</v>
       </c>
       <c r="E49" t="n">
         <v>0.3026</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1563</v>
+        <v>0.1609</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0771</v>
+        <v>0.0794</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3582</v>
+        <v>-0.3798</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1563</v>
+        <v>0.1609</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.2419</v>
+        <v>-1.2373</v>
       </c>
       <c r="G50" t="n">
         <v>1.3982</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.2419</v>
+        <v>-1.2373</v>
       </c>
       <c r="I50" t="n">
         <v>-1.2477</v>
@@ -2756,7 +2756,7 @@
         <v>0.0605</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3718</v>
+        <v>-0.395</v>
       </c>
       <c r="E51" t="n">
         <v>0.1227</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.1215</v>
+        <v>0.1188</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0599</v>
+        <v>0.0586</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3723</v>
+        <v>-0.3966</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1215</v>
+        <v>0.1188</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1819</v>
+        <v>0.1792</v>
       </c>
       <c r="G52" t="n">
         <v>-0.0604</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1819</v>
+        <v>0.1792</v>
       </c>
       <c r="I52" t="n">
         <v>0.1853</v>
@@ -2848,7 +2848,7 @@
         <v>-0.025</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4418</v>
+        <v>-0.4641</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0507</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1391</v>
+        <v>-0.1408</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0694</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4776</v>
+        <v>-0.5</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1391</v>
+        <v>-0.1408</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4561</v>
+        <v>0.4544</v>
       </c>
       <c r="G54" t="n">
         <v>-0.5952</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4561</v>
+        <v>0.4544</v>
       </c>
       <c r="I54" t="n">
         <v>0.4582</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2417</v>
+        <v>-0.2239</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1192</v>
+        <v>-0.1104</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.519</v>
+        <v>-0.5331</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2417</v>
+        <v>-0.2239</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.9608</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="G55" t="n">
         <v>0.7191</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.9608</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="I55" t="n">
         <v>-0.9834000000000001</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1517</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5456</v>
+        <v>-0.5665</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3076</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1749</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5646</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3546</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2177</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5997</v>
+        <v>-0.6198</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4415</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2263</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6067</v>
+        <v>-0.6267</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4588</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2777</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6488</v>
+        <v>-0.6682</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5631</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5689</v>
+        <v>-0.571</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2806</v>
+        <v>-0.2816</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6512</v>
+        <v>-0.6714</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5689</v>
+        <v>-0.571</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5735</v>
+        <v>0.5714</v>
       </c>
       <c r="G61" t="n">
         <v>-1.1424</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5735</v>
+        <v>0.5714</v>
       </c>
       <c r="I61" t="n">
         <v>0.5762</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3608</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7169</v>
+        <v>-0.7353</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7315</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4228</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7677</v>
+        <v>-0.7854</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8572</v>
@@ -3354,7 +3354,7 @@
         <v>-0.521</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8481</v>
+        <v>-0.8648</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0564</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5308</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8561</v>
+        <v>-0.8727</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0762</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5525</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8739</v>
+        <v>-0.8902</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1203</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1662</v>
+        <v>-1.1489</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5752</v>
+        <v>-0.5666</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8925</v>
+        <v>-0.9016</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.1662</v>
+        <v>-1.1489</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.1662</v>
+        <v>-1.1489</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.1662</v>
+        <v>-1.1489</v>
       </c>
       <c r="I67" t="n">
         <v>-1.1881</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5815</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.9136</v>
       </c>
       <c r="E68" t="n">
         <v>-1.179</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5966</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.91</v>
+        <v>-0.9258</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2096</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.3438</v>
+        <v>-1.3515</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.6666</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9823</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3438</v>
+        <v>-1.3515</v>
       </c>
       <c r="F70" t="n">
-        <v>1.0343</v>
+        <v>1.0266</v>
       </c>
       <c r="G70" t="n">
         <v>-2.3781</v>
       </c>
       <c r="H70" t="n">
-        <v>1.0343</v>
+        <v>1.0266</v>
       </c>
       <c r="I70" t="n">
         <v>1.0439</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6695</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9698</v>
+        <v>-0.9847</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3575</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3845</v>
+        <v>-1.3751</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6828</v>
+        <v>-0.6782</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9807</v>
+        <v>-0.9918</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3845</v>
+        <v>-1.3751</v>
       </c>
       <c r="F72" t="n">
-        <v>-2.5323</v>
+        <v>-2.5229</v>
       </c>
       <c r="G72" t="n">
         <v>1.1478</v>
       </c>
       <c r="H72" t="n">
-        <v>-2.5323</v>
+        <v>-2.5229</v>
       </c>
       <c r="I72" t="n">
         <v>-2.5441</v>
@@ -3768,7 +3768,7 @@
         <v>-0.732</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0209</v>
+        <v>-1.0352</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4842</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.5151</v>
+        <v>-1.4983</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7473</v>
+        <v>-0.739</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0334</v>
+        <v>-1.0408</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.5151</v>
+        <v>-1.4983</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.5151</v>
+        <v>-1.4983</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.5151</v>
+        <v>-1.4983</v>
       </c>
       <c r="I74" t="n">
         <v>-1.5364</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7819</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0618</v>
+        <v>-1.0755</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5853</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9706</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2164</v>
+        <v>-1.2279</v>
       </c>
       <c r="E76" t="n">
         <v>-1.9679</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.2617</v>
+        <v>-2.2365</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.1155</v>
+        <v>-1.103</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.335</v>
+        <v>-1.3349</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.2617</v>
+        <v>-2.2365</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.2617</v>
+        <v>-2.2365</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.2617</v>
+        <v>-2.2365</v>
       </c>
       <c r="I77" t="n">
         <v>-2.2934</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4871</v>
+        <v>-2.4818</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.2266</v>
+        <v>-1.224</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4261</v>
+        <v>-1.4327</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4871</v>
+        <v>-2.4818</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7178</v>
+        <v>-0.7125</v>
       </c>
       <c r="G78" t="n">
         <v>-1.7693</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.7178</v>
+        <v>-0.7125</v>
       </c>
       <c r="I78" t="n">
         <v>-0.7245</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.6747</v>
+        <v>-3.6682</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.8124</v>
+        <v>-1.8092</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.9059</v>
+        <v>-1.9053</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.6747</v>
+        <v>-3.6682</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.7566</v>
+        <v>-1.7501</v>
       </c>
       <c r="G79" t="n">
         <v>-1.9181</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.7566</v>
+        <v>-1.7501</v>
       </c>
       <c r="I79" t="n">
         <v>-1.7648</v>
@@ -4090,7 +4090,7 @@
         <v>-2.3147</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.3173</v>
+        <v>-2.3136</v>
       </c>
       <c r="E80" t="n">
         <v>-4.6931</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-7.4379</v>
+        <v>-7.3572</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.6684</v>
+        <v>-3.6286</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.4261</v>
+        <v>-3.375</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.4379</v>
+        <v>-7.3572</v>
       </c>
       <c r="F81" t="n">
-        <v>-5.4379</v>
+        <v>-5.3572</v>
       </c>
       <c r="G81" t="n">
         <v>-2</v>
       </c>
       <c r="H81" t="n">
-        <v>-5.4379</v>
+        <v>-5.3572</v>
       </c>
       <c r="I81" t="n">
         <v>-5.5398</v>
